--- a/output/pdf_financials_xlsx/GWM.xlsx
+++ b/output/pdf_financials_xlsx/GWM.xlsx
@@ -5187,43 +5187,43 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.020433</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.005196</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.006577</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.023485</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.100739</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.035392</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.017119</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.025629</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>-0.013041</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>-0.066159</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>0.075958</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>-0.09121899999999999</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>0.025911</v>
       </c>
     </row>
     <row r="104">
@@ -5325,43 +5325,43 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.104924</v>
+        <v>0.084491</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.024156</v>
+        <v>-0.029352</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.019494</v>
+        <v>-0.026071</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.048791</v>
+        <v>0.07227600000000001</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.035575</v>
+        <v>-0.065164</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.299247</v>
+        <v>0.334639</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.246662</v>
+        <v>-0.263781</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.389103</v>
+        <v>0.363474</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.108471</v>
+        <v>0.09543</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.728308</v>
+        <v>-0.794467</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.473946</v>
+        <v>0.5499039999999999</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.398863</v>
+        <v>0.307644</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.042602</v>
+        <v>0.068513</v>
       </c>
     </row>
     <row r="107">
@@ -6966,7 +6966,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E3" s="5" t="n">
         <v>0.030433</v>
       </c>
@@ -9148,7 +9152,11 @@
           <t>Prepaids and deposits 32,055 67,447</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -11122,7 +11130,11 @@
           <t>Prepaids and deposits 30,433</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E57" s="5" t="n">
         <v>0.01</v>
       </c>
@@ -12315,7 +12327,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>-0.020433</v>
       </c>
@@ -14778,7 +14794,11 @@
           <t>Prepaids and deposits 35,392</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GWM.xlsx
+++ b/output/pdf_financials_xlsx/GWM.xlsx
@@ -912,40 +912,40 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.015911</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.020637</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.019126</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017657</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.032101</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02202</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.024025</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001611</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000535</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.137983</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.175738</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.150002</v>
       </c>
     </row>
     <row r="13">
@@ -1664,40 +1664,40 @@
         <v>-0.107645</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.998636</v>
+        <v>-1.982725</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.186214</v>
+        <v>0.206851</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.777218</v>
+        <v>0.7963440000000001</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-2.412663</v>
+        <v>-2.395006</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-5.974787</v>
+        <v>-5.942686</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-5.376866</v>
+        <v>-5.354846</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-6.03958</v>
+        <v>-6.015555</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-16.188659</v>
+        <v>-16.187048</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-10.7408</v>
+        <v>-10.740265</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.402778</v>
+        <v>-5.264795</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-5.774718</v>
+        <v>-5.59898</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-8.409594999999999</v>
+        <v>-8.259593000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1756,40 +1756,40 @@
         <v>-0.107645</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.998636</v>
+        <v>-1.982725</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.186214</v>
+        <v>0.206851</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.777218</v>
+        <v>0.7963440000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-2.412663</v>
+        <v>-2.395006</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-5.974787</v>
+        <v>-5.942686</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-5.376866</v>
+        <v>-5.354846</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-6.03958</v>
+        <v>-6.015555</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-16.188659</v>
+        <v>-16.187048</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-10.7408</v>
+        <v>-10.740265</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.402778</v>
+        <v>-5.264795</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-5.774718</v>
+        <v>-5.59898</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-8.409594999999999</v>
+        <v>-8.259593000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1996,22 +1996,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>11.883874</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>11.064042</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>11.112093</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>10.037068</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>13.892136</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.471382</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>7.058093</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>11.883874</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>11.064042</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>11.112093</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>10.037068</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>13.892136</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.471382</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>7.058093</v>
@@ -2640,22 +2640,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>11.914307</v>
+        <v>0.030433</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>11.20846</v>
+        <v>0.144418</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>11.154299</v>
+        <v>0.042206</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>10.055789</v>
+        <v>0.018721</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>13.914195</v>
+        <v>0.022059</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.503437</v>
+        <v>0.032055</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.049174</v>
@@ -8842,7 +8842,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11047,7 +11047,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -18705,7 +18705,7 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -22521,7 +22521,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">

--- a/output/pdf_financials_xlsx/GWM.xlsx
+++ b/output/pdf_financials_xlsx/GWM.xlsx
@@ -5110,28 +5110,28 @@
         <v>0</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>-0.262997</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>-0.036189</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>-0.292223</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0</v>
+        <v>0.796988</v>
       </c>
       <c r="K101" s="3" t="n">
-        <v>0</v>
+        <v>0.327511</v>
       </c>
       <c r="L101" s="3" t="n">
-        <v>0</v>
+        <v>0.1022</v>
       </c>
       <c r="M101" s="3" t="n">
-        <v>0</v>
+        <v>0.218673</v>
       </c>
       <c r="N101" s="3" t="n">
-        <v>0</v>
+        <v>0.138875</v>
       </c>
     </row>
     <row r="102">
@@ -5340,28 +5340,28 @@
         <v>-0.065164</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.334639</v>
+        <v>0.071642</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>-0.263781</v>
+        <v>-0.29997</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.363474</v>
+        <v>0.07125099999999999</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.09543</v>
+        <v>0.892418</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>-0.794467</v>
+        <v>-0.466956</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0.5499039999999999</v>
+        <v>0.652104</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0.307644</v>
+        <v>0.526317</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.068513</v>
+        <v>0.207388</v>
       </c>
     </row>
     <row r="107">
@@ -12388,7 +12388,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
